--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="21480" yWindow="-1905" windowWidth="21840" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RUP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUP" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -196,421 +196,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>16</col>
-      <colOff>100853</colOff>
-      <row>0</row>
-      <rowOff>224118</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>720064</colOff>
-      <row>0</row>
-      <rowOff>643276</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="16976912" y="224118"/>
-          <a:ext cx="619211" cy="419158"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>40822</colOff>
-      <row>0</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>693964</colOff>
-      <row>0</row>
-      <rowOff>556581</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="22547036" y="95250"/>
-          <a:ext cx="653142" cy="461331"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>21</col>
-      <colOff>748393</colOff>
-      <row>0</row>
-      <rowOff>176893</rowOff>
-    </from>
-    <to>
-      <col>22</col>
-      <colOff>721178</colOff>
-      <row>0</row>
-      <rowOff>585107</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 3"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="23567572" y="176893"/>
-          <a:ext cx="734785" cy="408214"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>25</col>
-      <colOff>680357</colOff>
-      <row>0</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>26</col>
-      <colOff>747148</colOff>
-      <row>0</row>
-      <rowOff>540244</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 4"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="26996571" y="136071"/>
-          <a:ext cx="828791" cy="404173"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>81643</colOff>
-      <row>0</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>700854</colOff>
-      <row>0</row>
-      <rowOff>518463</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 5"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="27921857" y="136071"/>
-          <a:ext cx="619211" cy="382392"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>16</col>
-      <colOff>100853</colOff>
-      <row>1</row>
-      <rowOff>224118</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>720064</colOff>
-      <row>2</row>
-      <rowOff>71776</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="18188828" y="224118"/>
-          <a:ext cx="619211" cy="419158"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>40822</colOff>
-      <row>1</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>693964</colOff>
-      <row>1</row>
-      <rowOff>556581</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="22538872" y="95250"/>
-          <a:ext cx="653142" cy="461331"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>21</col>
-      <colOff>748393</colOff>
-      <row>1</row>
-      <rowOff>176893</rowOff>
-    </from>
-    <to>
-      <col>22</col>
-      <colOff>721178</colOff>
-      <row>2</row>
-      <rowOff>13607</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 3"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="24008443" y="176893"/>
-          <a:ext cx="734785" cy="408214"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>25</col>
-      <colOff>680357</colOff>
-      <row>1</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>26</col>
-      <colOff>747148</colOff>
-      <row>1</row>
-      <rowOff>540244</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 4"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="26988407" y="136071"/>
-          <a:ext cx="828791" cy="404173"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>81643</colOff>
-      <row>1</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>700854</colOff>
-      <row>1</row>
-      <rowOff>518463</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 5"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="27913693" y="136071"/>
-          <a:ext cx="619211" cy="382392"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -62843,6 +62428,5 @@
     <mergeCell ref="A325:A335"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,60 @@
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFBE00"/>
+        <bgColor rgb="00FFBE00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C70000"/>
+        <bgColor rgb="00C70000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF3300"/>
+        <bgColor rgb="00FF3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFEFE"/>
+        <bgColor rgb="00FEFEFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDAA66"/>
+        <bgColor rgb="00CDAA66"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000A884"/>
+        <bgColor rgb="0000A884"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CAFF80"/>
+        <bgColor rgb="00CAFF80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D491E6"/>
+        <bgColor rgb="00D491E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +242,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +601,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AQ395"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18.42578125" customWidth="1" min="1" max="1"/>
     <col width="18.140625" customWidth="1" min="4" max="4"/>
@@ -626,7 +707,7 @@
           <t>RUP</t>
         </is>
       </c>
-      <c r="O2" s="18" t="inlineStr">
+      <c r="O2" s="21" t="inlineStr">
         <is>
           <t>zone voor wonen met beperkte nevenfuncties</t>
         </is>
@@ -666,7 +747,7 @@
           <t>zone voor openbare wegeninfrastructuur</t>
         </is>
       </c>
-      <c r="W2" s="18" t="inlineStr">
+      <c r="W2" s="22" t="inlineStr">
         <is>
           <t>zone voor gemengde functies op waardevolle site</t>
         </is>
@@ -676,7 +757,7 @@
           <t>zone voor wonen:met beperkte functies - aaneengesloten en gestapelde bebouwing</t>
         </is>
       </c>
-      <c r="Y2" s="18" t="inlineStr">
+      <c r="Y2" s="23" t="inlineStr">
         <is>
           <t>zone voor gemengde functies</t>
         </is>
@@ -691,7 +772,7 @@
           <t>zone voor wonen:met beperkte nevenfuncties - open en halfopen bebouwing</t>
         </is>
       </c>
-      <c r="AB2" s="18" t="inlineStr">
+      <c r="AB2" s="24" t="inlineStr">
         <is>
           <t>zone voor recreatie</t>
         </is>
@@ -716,7 +797,7 @@
           <t>zone voor buffergroen</t>
         </is>
       </c>
-      <c r="AG2" s="18" t="inlineStr">
+      <c r="AG2" s="25" t="inlineStr">
         <is>
           <t>zone voor landbouw in de ruime zin</t>
         </is>
@@ -726,7 +807,7 @@
           <t>zone voor groenbuffer</t>
         </is>
       </c>
-      <c r="AI2" s="18" t="inlineStr">
+      <c r="AI2" s="26" t="inlineStr">
         <is>
           <t>zone voor voetgangers-, fietsersverbinding en garageweg</t>
         </is>
@@ -746,17 +827,17 @@
           <t>Agrarisch gebied</t>
         </is>
       </c>
-      <c r="AM2" s="18" t="inlineStr">
+      <c r="AM2" s="27" t="inlineStr">
         <is>
           <t>zone voor tuin</t>
         </is>
       </c>
-      <c r="AN2" s="18" t="inlineStr">
+      <c r="AN2" s="28" t="inlineStr">
         <is>
           <t>zone voor kleine bedrijvigheid</t>
         </is>
       </c>
-      <c r="AO2" s="18" t="inlineStr">
+      <c r="AO2" s="29" t="inlineStr">
         <is>
           <t>zone voor laden en lossen</t>
         </is>

--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -277,6 +277,36 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>28</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="171450" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -601,7 +631,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AQ395"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="18.42578125" customWidth="1" min="1" max="1"/>
     <col width="18.140625" customWidth="1" min="4" max="4"/>
@@ -84529,5 +84559,6 @@
     <mergeCell ref="A325:A335"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -302,6 +302,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -940,7 +943,7 @@
       </c>
       <c r="O3" s="19" t="inlineStr">
         <is>
-          <t>2.1 Bestemming
+          <t>Bestemming
 De zone is bestemd voor wonen met beperkte nevenfuncties. Binnen deze zone
 zijn wonen en de bijhorende openbare en private groene en verharde ruimten
 de hoofdfuncties. De beperkte nevenfuncties mogen de woonfunctie van de
@@ -1142,7 +1145,7 @@
       </c>
       <c r="AE3" s="19" t="inlineStr">
         <is>
-          <t>2.1 Bestemming
+          <t>Bestemming
 De zone is bestemd voor wonen met beperkte nevenfuncties. Binnen deze
 zone vormen wonen en de bijhorende openbare en private groene en verharde
 ruimten de hoofdfuncties.

--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="P3" s="19" t="inlineStr">
         <is>
-          <t>5 Bestemming
+          <t>Bestemming
 De zone is bestemd voor gemeenschapsvoorzieningen.
 Alle werken, handelingen, en wijzigingen die nodig of nuttig zijn voor deze
 bestemmingen zijn toegelaten.</t>
@@ -966,7 +966,7 @@
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
-          <t>13 Bestemming
+          <t>Bestemming
 De zone is bestemd voor service-fl ats.
 Alle werken, handelingen, en wijzigingen die nodig of nuttig zijn voor deze
 bestemming zijn toegelaten.
@@ -977,7 +977,7 @@
       </c>
       <c r="R3" s="19" t="inlineStr">
         <is>
-          <t>26 Bestemming
+          <t>Bestemming
 Het gebied is bestemd voor cultureel-recreatieve functies in open lucht.
 Alle werken, handelingen en wijzigingen die nodig of nuttig zijn voor het
 realiseren van de bestemming, zijn toegelaten.</t>
@@ -985,7 +985,7 @@
       </c>
       <c r="S3" s="19" t="inlineStr">
         <is>
-          <t>26 Bestemming
+          <t>Bestemming
 Het gebied is bestemd voor cultureel-recreatieve functies in open lucht.
 Alle werken, handelingen en wijzigingen die nodig of nuttig zijn voor het
 realiseren van de bestemming, zijn toegelaten.</t>
@@ -993,7 +993,7 @@
       </c>
       <c r="T3" s="19" t="inlineStr">
         <is>
-          <t>9 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor meergezinswoongebouwen (appartementen of
 urban-villa’s) en openbaar groen.
 10 Minimum 40 % van de zone moet ingericht worden als openbaar groengebied.
@@ -1029,7 +1029,7 @@
       </c>
       <c r="U3" s="19" t="inlineStr">
         <is>
-          <t>1 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor de realisatie van een sociaal woonproject met
 aanééngesloten ééngezinswoningen (rijwoningen).
 Indien in de aanpalende zone 2 (zone voor meergezinswoongebouwen en
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB3" s="19" t="inlineStr">
         <is>
-          <t>3.1 Bestemming
+          <t>Bestemming
 De zone is bestemd voor recreatie.
 Alle werken, handelingen en wijzigingen die nodig of nuttig zijn voor het
 realiseren van deze bestemming, zijn toegelaten.
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AC3" s="19" t="inlineStr">
         <is>
-          <t>3.1 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor openbare wegeninfrastructuur en aanhorigheden.
 3.2 In deze zone zijn alle bovengrondse en ondergrondse werken, handelingen en
 wijzigingen toegelaten voor de aanleg, het functioneren of aanpassing van die
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AD3" s="19" t="inlineStr">
         <is>
-          <t>4.1 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor gemeenschapsvoorzieningen en openbare
 nutsvoorzieningen, met specifi ek het gemeentelijk containerpark (of
 afvalstoffenpark) en de gemeentelijke technische diensten en depot.
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AF3" s="19" t="inlineStr">
         <is>
-          <t>7.1 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor openbare wegeninfrastructuur en aanhorigheden.
 In deze zone zijn alle bovengrondse en ondergrondse werken, handelingen en
 wijzigingen toegelaten voor de aanleg, het functioneren of aanpassing van die
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AG3" s="19" t="inlineStr">
         <is>
-          <t>5.1 Bestemming
+          <t>Bestemming
 De zone is bestemd voor de ontwikkeling en de instandhouding van een
 landschappelijke groenbuffer, eventueel gecombineerd met waterbufferbekkens
 en -infi ltratiezones.
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AH3" s="19" t="inlineStr">
         <is>
-          <t>5.1 Bestemming
+          <t>Bestemming
 De zone is bestemd voor de ontwikkeling en de instandhouding van een
 landschappelijke groenbuffer, eventueel gecombineerd met waterbufferbekkens
 en -infi ltratiezones.
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AI3" s="19" t="inlineStr">
         <is>
-          <t>19 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor gemeenschapsvoorzieningen binnen het oude
 stationsgebouw.
 20 De erfgoedwaarde, het karakter en de architecturale verschijningsvorm van het
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AQ3" s="19" t="inlineStr">
         <is>
-          <t>9 Bestemming
+          <t>Bestemming
 Deze zone is bestemd voor meergezinswoongebouwen (appartementen of
 urban-villa’s) en openbaar groen.
 10 Minimum 40 % van de zone moet ingericht worden als openbaar groengebied.

--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +122,24 @@
         <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7800"/>
+        <bgColor rgb="00FF7800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7700"/>
+        <bgColor rgb="00FF7700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9680"/>
+        <bgColor rgb="00FF9680"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -183,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -268,6 +286,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -760,22 +787,22 @@
           <t>zone voor cultureel - recreatieve functies in open lucht</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="S2" s="29" t="inlineStr">
         <is>
           <t>zone voor openbare wegenis</t>
         </is>
       </c>
-      <c r="T2" s="18" t="inlineStr">
+      <c r="T2" s="29" t="inlineStr">
         <is>
           <t>zone voor openbare wegenis en plein</t>
         </is>
       </c>
-      <c r="U2" s="18" t="inlineStr">
+      <c r="U2" s="30" t="inlineStr">
         <is>
           <t>zone voor sociaal woonproject: aanééngesloten ééngezinswoningen</t>
         </is>
       </c>
-      <c r="V2" s="18" t="inlineStr">
+      <c r="V2" s="29" t="inlineStr">
         <is>
           <t>zone voor openbare wegeninfrastructuur</t>
         </is>
@@ -795,7 +822,7 @@
           <t>zone voor gemengde functies</t>
         </is>
       </c>
-      <c r="Z2" s="18" t="inlineStr">
+      <c r="Z2" s="31" t="inlineStr">
         <is>
           <t>zone voor sociale woningen</t>
         </is>
@@ -845,12 +872,12 @@
           <t>zone voor voetgangers-, fietsersverbinding en garageweg</t>
         </is>
       </c>
-      <c r="AJ2" s="18" t="inlineStr">
+      <c r="AJ2" s="28" t="inlineStr">
         <is>
           <t>zone voor bedrijvigheid</t>
         </is>
       </c>
-      <c r="AK2" s="18" t="inlineStr">
+      <c r="AK2" s="32" t="inlineStr">
         <is>
           <t>zone voor wonen in ruime zin</t>
         </is>
@@ -880,7 +907,7 @@
           <t>Gebied voor gemeenschaps- en openbare nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="AQ2" s="18" t="inlineStr">
+      <c r="AQ2" s="32" t="inlineStr">
         <is>
           <t>zone voor meergezinswoongebouwen en openbaar groen</t>
         </is>

--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +140,18 @@
         <bgColor rgb="00FF9680"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFBF00"/>
+        <bgColor rgb="00FFBF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9A300"/>
+        <bgColor rgb="00D9A300"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -201,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -295,6 +307,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -812,7 +830,7 @@
           <t>zone voor gemengde functies op waardevolle site</t>
         </is>
       </c>
-      <c r="X2" s="18" t="inlineStr">
+      <c r="X2" s="33" t="inlineStr">
         <is>
           <t>zone voor wonen:met beperkte functies - aaneengesloten en gestapelde bebouwing</t>
         </is>
@@ -827,7 +845,7 @@
           <t>zone voor sociale woningen</t>
         </is>
       </c>
-      <c r="AA2" s="18" t="inlineStr">
+      <c r="AA2" s="34" t="inlineStr">
         <is>
           <t>zone voor wonen:met beperkte nevenfuncties - open en halfopen bebouwing</t>
         </is>
@@ -847,7 +865,7 @@
           <t>zone voor gemeenschaps- en openbare nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="AE2" s="18" t="inlineStr">
+      <c r="AE2" s="23" t="inlineStr">
         <is>
           <t>zone zone voor gemengde functies</t>
         </is>

--- a/state/8580_avelgem_rup.xlsx
+++ b/state/8580_avelgem_rup.xlsx
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +152,36 @@
         <bgColor rgb="00D9A300"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4D2FF"/>
+        <bgColor rgb="00B4D2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000734C"/>
+        <bgColor rgb="0000734C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0038A800"/>
+        <bgColor rgb="0038A800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000C7BA"/>
+        <bgColor rgb="0000C7BA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD380"/>
+        <bgColor rgb="00FFD380"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -213,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -313,6 +343,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -790,17 +835,17 @@
           <t>zone voor wonen met beperkte nevenfuncties</t>
         </is>
       </c>
-      <c r="P2" s="18" t="inlineStr">
+      <c r="P2" s="35" t="inlineStr">
         <is>
           <t>zone voor gemeenschapsvoorzieningen</t>
         </is>
       </c>
-      <c r="Q2" s="18" t="inlineStr">
+      <c r="Q2" s="38" t="inlineStr">
         <is>
           <t>zone voor openbaar groen</t>
         </is>
       </c>
-      <c r="R2" s="18" t="inlineStr">
+      <c r="R2" s="39" t="inlineStr">
         <is>
           <t>zone voor cultureel - recreatieve functies in open lucht</t>
         </is>
@@ -860,7 +905,7 @@
           <t>perimeter woonuitbreidingsgebied</t>
         </is>
       </c>
-      <c r="AD2" s="18" t="inlineStr">
+      <c r="AD2" s="35" t="inlineStr">
         <is>
           <t>zone voor gemeenschaps- en openbare nutsvoorzieningen</t>
         </is>
@@ -870,7 +915,7 @@
           <t>zone zone voor gemengde functies</t>
         </is>
       </c>
-      <c r="AF2" s="18" t="inlineStr">
+      <c r="AF2" s="36" t="inlineStr">
         <is>
           <t>zone voor buffergroen</t>
         </is>
@@ -880,7 +925,7 @@
           <t>zone voor landbouw in de ruime zin</t>
         </is>
       </c>
-      <c r="AH2" s="18" t="inlineStr">
+      <c r="AH2" s="37" t="inlineStr">
         <is>
           <t>zone voor groenbuffer</t>
         </is>
